--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_851_USA_East_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_851_USA_East_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf9363d09ceb9446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6bad1baec0a84039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3e0fec0686644c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc6152fc51af84767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb58c297137a24f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rbfc42e2efb534315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R180371172b824e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rfb90f9a9eeb64184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R42116be6f0f74f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb176bb4363994bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3932a504fb0d4852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf129c048a2184bee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ851CommercialTable" displayName="EEZ851CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ851CommercialTable" displayName="EEZ851CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ851FunctionalTable" displayName="EEZ851FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ851FunctionalTable" displayName="EEZ851FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ851ValidationTable" displayName="EEZ851ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ851ValidationTable" displayName="EEZ851ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -24278,7 +24232,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b77ce49ed534e3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1dbbdd0eeb4f19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24288,20 +24242,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -24309,714 +24253,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.2815951021</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.340387399907897</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.97140244764262</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.2815951021</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>219.0172213268623</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$353,A2,'Species'!$U$2:$U$353))</x:f>
-        <x:v>1375.77750476237</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.340387399907897</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.97140244764262</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1375.4896891150797</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.28781564729024467</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0002092459504188</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00020924595041887275</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>29881.942217492597</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.205210740285292</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1604.0235501952984</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>29881.942217492597</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1784.0927092242218</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$353,A3,'Species'!$U$2:$U$353))</x:f>
-        <x:v>53312155.24768802</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.205210740285292</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1604.0235501952984</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>47931339.04243324</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5380816.205254778</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.112260919739613</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.11226091973961302</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>142586.87055546447</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6280783417138482</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>424.6961673255616</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>142586.87055546447</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>576.0317982587328</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$353,A4,'Species'!$U$2:$U$353))</x:f>
-        <x:v>82134571.45414935</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6280783417138482</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>424.6961673255616</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>60556097.43585173</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>21578474.01829762</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.356338584089837</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.3563385840898371</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>14749.2056133146</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.215404739004271</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1642.119426939311</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>14749.2056133146</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2151.484365047274</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$353,A5,'Species'!$U$2:$U$353))</x:f>
-        <x:v>31732685.273913853</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.215404739004271</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1642.119426939311</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>24219957.06954624</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7512728.204367612</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.310187511183246</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.31018751118324595</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>296330.8381888818</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.193210306187062</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>156.0307895721756</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>296330.8381888818</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>164.45956956039697</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$353,A6,'Species'!$U$2:$U$353))</x:f>
-        <x:v>48734442.09601515</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.193210306187062</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>156.0307895721756</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>46236734.65719584</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2497707.4388193116</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0540199790780553</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05401997907805526</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>164961.3857786492</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.048294895823839</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.176218808452226</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>164961.3857786492</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>13.691663872086338</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$353,A7,'Species'!$U$2:$U$353))</x:f>
-        <x:v>2258595.845954828</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.048294895823839</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.176218808452226</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1843644.5424076826</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>414951.30354714533</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2250712076012469</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.22507120760124688</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>161577.3635441399</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4998908993181024</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>316.14833527758265</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>161577.3635441399</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>558.0760127496867</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$353,A8,'Species'!$U$2:$U$353))</x:f>
-        <x:v>90172450.79732017</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4998908993181024</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>316.14833527758265</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>51082414.5030206</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>39090036.29429957</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7652347030696465</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7652347030696465</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>136325.1082484332</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9639353299960103</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>920.3125194804339</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>136325.1082484332</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1583.2034341448389</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$353,A9,'Species'!$U$2:$U$353))</x:f>
-        <x:v>215830379.5390863</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9639353299960103</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>920.3125194804339</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>125461703.84055842</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>90368675.69852789</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.7202889242869832</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.7202889242869831</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.0667341452</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.084834676087228</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>121.57231203390124</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.0667341452</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>134.74591354475604</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$353,A10,'Species'!$U$2:$U$353))</x:f>
-        <x:v>8.992153359602396</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.084834676087228</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>121.57231203390124</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8.113024323570073</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.8791290360323227</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1083602120454963</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10836021204549635</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>6870.076071529799</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7975400097501897</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>627.393492483237</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>6870.076071529799</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>630.3786432935655</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$353,A11,'Species'!$U$2:$U$353))</x:f>
-        <x:v>4330749.233294543</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7975400097501897</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>627.393492483237</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4310241.020142597</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>20508.213151945733</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0047580200402035</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.004758020040203518</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>36036.7525618867</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.098622448634266</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1254.9385158886305</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>36036.7525618867</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1607.8252292144048</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$353,A12,'Species'!$U$2:$U$353))</x:f>
-        <x:v>57940799.94795827</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.098622448634266</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1254.9385158886305</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>45223908.7774599</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>12716891.170498371</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2811984084143697</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.28119840841436977</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>13670.1963989351</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.45708861159076</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2864.762424166398</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>13670.1963989351</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2885.626420427152</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$353,A13,'Species'!$U$2:$U$353))</x:f>
-        <x:v>39447079.901195236</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.45708861159076</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2864.762424166398</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>39161864.97464408</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>285214.92655115575</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0072829760976865</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.007282976097686418</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e89e233d8e4de2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fbdf82a7fd54825"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25026,20 +24506,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -25047,1416 +24517,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>46228.965629956605</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.745555876160771</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>556.6162436830674</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>46228.965629956605</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>668.0101326753124</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$353,A2,'Species'!$U$2:$U$353))</x:f>
-        <x:v>30881417.463909768</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.745555876160771</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>556.6162436830674</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>25731793.198300075</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5149624.265609693</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2001269101583598</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.2001269101583598</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6649.848064854301</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.41088008074555</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>257.56098703645927</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6649.848064854301</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>259.9025501089254</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$353,A3,'Species'!$U$2:$U$353))</x:f>
-        <x:v>1728312.4698925356</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.41088008074555</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>257.56098703645927</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1712741.4312263622</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>15571.03866617335</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.009091295616656</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009091295616656</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.3580628597000002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.1131564249035915</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1297.6465753078285</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.3580628597000002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1328.2592320956587</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$353,A4,'Species'!$U$2:$U$353))</x:f>
-        <x:v>1803.8595311627564</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.1131564249035915</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1297.6465753078285</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1762.2856189424613</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>41.57391222029514</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0235909047735652</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.023590904773565274</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>7.0123260954</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>7.0123260954</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$353,A5,'Species'!$U$2:$U$353))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>15341.297926136123</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>15341.297926136123</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4960.209177225801</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6637592099685894</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>461.06187275013815</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4960.209177225801</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1030.7269123321726</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$353,A6,'Species'!$U$2:$U$353))</x:f>
-        <x:v>5112621.089763656</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6637592099685894</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>461.06187275013815</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2286963.33248415</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2825657.7572795064</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>2.2355500926244476</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.2355500926244476</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>39107.3196017269</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.405390732834638</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2543.259836219599</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>39107.3196017269</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2936.7277047714156</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$353,A7,'Species'!$U$2:$U$353))</x:f>
-        <x:v>114847548.93374163</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.405390732834638</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2543.259836219599</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>99460075.24527547</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>15387473.688466161</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1547100547684042</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1547100547684041</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>334.65321862630003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>334.65321862630003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$353,A8,'Species'!$U$2:$U$353))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>334653.21862630005</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>334653.21862630005</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>44590.557359056</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.437359274196734</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2737.532439308439</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>44590.557359056</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2811.5291563098826</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$353,A9,'Species'!$U$2:$U$353))</x:f>
-        <x:v>125367652.11109415</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.437359274196734</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2737.532439308439</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>122068097.25725943</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3299554.8538347185</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0270304438913378</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.027030443891337814</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>10664.5226860244</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7584613923551</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>573.4048900833826</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>10664.5226860244</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>593.9484150198781</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$353,A10,'Species'!$U$2:$U$353))</x:f>
-        <x:v>6334176.346307726</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7584613923551</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>573.4048900833826</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6115089.458571562</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>219086.88773616403</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0358272580017727</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03582725800177273</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8901.0130820903</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8429558671238815</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>696.555726728296</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8901.0130820903</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>866.8747864613265</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$353,A11,'Species'!$U$2:$U$353))</x:f>
-        <x:v>7716063.814826502</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8429558671238815</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>696.555726728296</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6200051.636013479</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1516012.1788130235</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2445160569320342</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.24451605693203418</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>21167.7656417375</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.367095089656983</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2328.6010537725488</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>21167.7656417375</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2357.060855976674</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$353,A12,'Species'!$U$2:$U$353))</x:f>
-        <x:v>49893711.802627414</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.367095089656983</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2328.6010537725488</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>49291281.379360296</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>602430.4232671186</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0122218454543845</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.012221845454384431</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>121502.4381549372</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.727327081110431</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>533.7367184055117</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>121502.4381549372</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>654.6811703378658</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$353,A13,'Species'!$U$2:$U$353))</x:f>
-        <x:v>79545358.41017844</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.727327081110431</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>533.7367184055117</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>64850312.61908483</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>14695045.79109361</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.22659945954939</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.22659945954939004</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1565.3618827195</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.409107316762491</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>2565.117814154341</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1565.3618827195</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>2750.1015838053636</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$353,A14,'Species'!$U$2:$U$353))</x:f>
-        <x:v>4304904.192895443</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.409107316762491</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>2565.117814154341</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>4015337.6509619677</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>289566.5419334755</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0721151163624068</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0721151163624068</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3348.7919337123994</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.5522689763735906</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>356.67196660192417</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3348.7919337123994</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>525.9109496836882</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$353,A15,'Species'!$U$2:$U$353))</x:f>
-        <x:v>1761166.3461517624</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.5522689763735906</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>356.67196660192417</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1194420.2047378619</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>566746.1414139005</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4744947709070977</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.47449477090709774</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>154378.4932207306</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.481285380478453</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>302.8903105416567</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>154378.4932207306</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>483.8161190039864</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$353,A16,'Species'!$U$2:$U$353))</x:f>
-        <x:v>74690803.4477371</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.481285380478453</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>302.8903105416567</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>46759749.75258013</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>27931053.69515697</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.5973311200968474</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5973311200968473</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>113101.07677870241</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3319249201568466</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>214.74591941727755</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>113101.07677870241</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>336.2839836250001</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$353,A17,'Species'!$U$2:$U$353))</x:f>
-        <x:v>38034080.651419036</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3319249201568466</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>214.74591941727755</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>24287994.719926547</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>13746085.931492489</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.5659621590832618</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5659621590832618</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>15658.615604149798</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.7285633791229946</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>535.2582614271304</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>15658.615604149798</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>735.2966742360375</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$353,A18,'Species'!$U$2:$U$353))</x:f>
-        <x:v>11513727.976871867</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.7285633791229946</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>535.2582614271304</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>8381403.364632956</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>3132324.612238911</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.3737231673464607</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.3737231673464607</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>167970.2303086857</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.056069223418153</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>11.378086298861614</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>167970.2303086857</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>14.074452265110807</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$353,A19,'Species'!$U$2:$U$353))</x:f>
-        <x:v>2364088.9884392656</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.056069223418153</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>11.378086298861614</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1911179.7760918867</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>452909.21234737895</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2369788640572157</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.2369788640572156</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>21084.432400527297</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.05614149317021</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>113.79979852501833</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>21084.432400527297</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>122.80212219069031</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$353,A20,'Species'!$U$2:$U$353))</x:f>
-        <x:v>2589213.043970903</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.05614149317021</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>113.79979852501833</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2399404.159194375</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>189808.884776528</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0791066749005962</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.07910667490059628</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>6143.634161012299</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.8964161257011196</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>787.800270696131</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>6143.634161012299</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>812.4140986351667</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$353,A21,'Species'!$U$2:$U$353))</x:f>
-        <x:v>4991175.009263026</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.8964161257011196</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>787.800270696131</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>4839956.655103487</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>151218.35415953863</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0312437414083215</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.031243741408321625</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>4.1196393723</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>4.1196393723</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$353,A22,'Species'!$U$2:$U$353))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>12730.902735821852</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>12730.902735821852</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>196937.8219326436</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.1647330669807685</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>146.12787438723797</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>196937.8219326436</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>155.3881352038648</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$353,A23,'Species'!$U$2:$U$353))</x:f>
-        <x:v>30601800.901224274</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.1647330669807685</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>146.12787438723797</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>28778105.30546958</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>1823695.5957546942</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0633709403866862</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.06337094038668632</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>72.5676172895</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>4.259161502150644</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>1816.1909285693778</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>72.5676172895</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>2057.194771031152</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$353,A24,'Species'!$U$2:$U$353))</x:f>
-        <x:v>149285.72283414923</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>4.259161502150644</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>1816.1909285693778</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>131796.64822908424</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>17489.07460506499</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.1326974156024523</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.1326974156024522</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>14410.814789114098</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>4.220387599626841</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>1661.0687185699924</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>14410.814789114098</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>2178.2768541966952</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$353,A25,'Species'!$U$2:$U$353))</x:f>
-        <x:v>31390744.305242673</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>4.220387599626841</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>1661.0687185699924</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>23937353.65530325</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>7453390.649939422</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.3113707035985636</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.3113707035985636</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>4204.4642341248</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.6097823657256214</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>407.1761819570117</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>4204.4642341248</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>407.4031086102661</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$353,A26,'Species'!$U$2:$U$353))</x:f>
-        <x:v>1712911.799023125</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.6097823657256214</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>407.1761819570117</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>1711957.6940257475</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>954.1049973776098</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0005573180930272</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0005573180930271635</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01a6a93b5fb4450f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddd16d2a2cd8492e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26631,7 +25182,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -26730,7 +25281,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>625895294.1062338</x:v>
+        <x:v>446029289.4659738</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26744,7 +25295,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>625895294.1062338</x:v>
+        <x:v>526429552.84873974</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26758,7 +25309,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-179866004.64025992</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26772,7 +25323,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-99465741.25749397</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26783,9 +25334,9 @@
         <x:v>EEZ_851</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -26797,47 +25348,19 @@
         <x:v>EEZ_851</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_851</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_851</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b5269b1af574274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e7c644005a64bc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26884,7 +25407,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
